--- a/packages/calculators/src/modules/test/5.5-leaching-runoff.xlsx
+++ b/packages/calculators/src/modules/test/5.5-leaching-runoff.xlsx
@@ -1,21 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B07FA9-B46A-9C4B-9E75-B0DE4A6F6AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3C494A-7CBA-D648-B042-D1F813BBA7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10480" yWindow="5200" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="5.5.1.1 (feedlot local)" sheetId="2" r:id="rId1"/>
     <sheet name="5.5.1.1 (inorganic)" sheetId="4" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -791,6 +789,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1289,8 +1309,8 @@
         <v>2</v>
       </c>
       <c r="AS7">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="AV7" s="8"/>
     </row>
@@ -1622,11 +1642,11 @@
       </c>
       <c r="AO11">
         <f>$AS$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP11">
         <f>(AI11+AM11)*AN11*AO11*10^-3</f>
-        <v>5.3926421050884115E-3</v>
+        <v>5.3877397031746955E-3</v>
       </c>
       <c r="AR11" s="2"/>
       <c r="AS11" s="2"/>
@@ -1774,11 +1794,11 @@
       </c>
       <c r="AO12">
         <f t="shared" ref="AO12:AO20" si="19">$AS$7</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP12">
         <f t="shared" ref="AP12:AP20" si="20">(AI12+AM12)*AN12*AO12*10^-3</f>
-        <v>6.7408026313605148E-3</v>
+        <v>6.7346746289683691E-3</v>
       </c>
       <c r="AR12" s="2"/>
       <c r="AS12" s="2"/>
@@ -1926,11 +1946,11 @@
       </c>
       <c r="AO13">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP13">
         <f t="shared" si="20"/>
-        <v>7.677206166592513E-3</v>
+        <v>7.670226888259247E-3</v>
       </c>
       <c r="AR13" s="2"/>
       <c r="AS13" s="2"/>
@@ -2078,11 +2098,11 @@
       </c>
       <c r="AO14">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP14">
         <f t="shared" si="20"/>
-        <v>8.5546011570602279E-3</v>
+        <v>8.5468242469174463E-3</v>
       </c>
       <c r="AR14" s="2"/>
       <c r="AS14" s="2"/>
@@ -2230,11 +2250,11 @@
       </c>
       <c r="AO15">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP15">
         <f t="shared" si="20"/>
-        <v>7.3812332660318199E-3</v>
+        <v>7.3745230539717915E-3</v>
       </c>
       <c r="AR15" s="2"/>
       <c r="AS15" s="2"/>
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AO16">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP16">
         <f t="shared" si="20"/>
@@ -2535,7 +2555,7 @@
       </c>
       <c r="AO17">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP17">
         <f t="shared" si="20"/>
@@ -2691,7 +2711,7 @@
       </c>
       <c r="AO18">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP18">
         <f t="shared" si="20"/>
@@ -2844,7 +2864,7 @@
       </c>
       <c r="AO19">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP19">
         <f t="shared" si="20"/>
@@ -3003,7 +3023,7 @@
       </c>
       <c r="AO20">
         <f t="shared" si="19"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AP20">
         <f t="shared" si="20"/>
@@ -3345,21 +3365,21 @@
       </c>
       <c r="N4">
         <f>$S$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" s="13">
         <f>(O4+L4)*M4*N4*10^-3</f>
-        <v>9.5417142857142848E-5</v>
+        <v>9.5330399999999984E-5</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
       </c>
       <c r="S4">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="17">
@@ -3401,14 +3421,14 @@
       </c>
       <c r="N5">
         <f>$S$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5" s="13">
         <f t="shared" ref="P5:P6" si="5">(O5+L5)*M5*N5*10^-3</f>
-        <v>2.9869714285714281E-5</v>
+        <v>2.9842559999999998E-5</v>
       </c>
       <c r="R5" t="s">
         <v>116</v>
@@ -3460,14 +3480,14 @@
       </c>
       <c r="N6">
         <f>$S$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6" s="13">
         <f t="shared" si="5"/>
-        <v>3.1114285714285714E-5</v>
+        <v>3.1086E-5</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>114</v>
@@ -3519,7 +3539,7 @@
       </c>
       <c r="N7">
         <f>$S$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -3609,14 +3629,14 @@
       </c>
       <c r="N10">
         <f>$S$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10" s="11">
         <f>(O10+L10)*M10*N10*10^-3</f>
-        <v>6.0984000000000003E-3</v>
+        <v>6.0928560000000007E-3</v>
       </c>
       <c r="R10" t="s">
         <v>3</v>
@@ -3671,14 +3691,14 @@
       </c>
       <c r="N11">
         <f>$S$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11" s="11">
         <f>(O11+L11)*M11*N11*10^-3</f>
-        <v>4.9782857142857137E-3</v>
+        <v>4.9737599999999998E-3</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>4</v>
@@ -3736,7 +3756,7 @@
       </c>
       <c r="N12">
         <f>$S$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="O12">
         <v>0</v>
